--- a/templates/tabs/Crosstab_Config.xlsx
+++ b/templates/tabs/Crosstab_Config.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="346">
   <si>
     <t xml:space="preserve">TURAS Crosstab Configuration</t>
   </si>
@@ -598,6 +598,78 @@
   </si>
   <si>
     <t xml:space="preserve">warm, cool, research, teal, red, or brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 1st banner series in bar charts (e.g., Total). Leave blank to auto-generate. You can define some colours and leave others blank — blanks are auto-filled with distinct hues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #1B365D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 2nd banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #3A6EA5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 3rd banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #E87722)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 4th banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #5B9A7D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 5th banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #8E4585)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 6th banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #C14D00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 7th banner series in bar charts. Leave blank to auto-generate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #4A7C6F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart_series_colour_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom colour for 8th banner series in bar charts. Leave blank to auto-generate. If all 8 set and more than 8 series exist, colours cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hex colour code (e.g. #D4918E)</t>
   </si>
   <si>
     <t xml:space="preserve">embed_frequencies</t>
@@ -2753,25 +2825,25 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="15" t="s">
         <v>194</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>195</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>36</v>
@@ -2780,32 +2852,32 @@
         <v>4</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="s">
-        <v>199</v>
+      <c r="A85" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>201</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>36</v>
@@ -2814,15 +2886,15 @@
         <v>4</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>36</v>
@@ -2831,15 +2903,15 @@
         <v>4</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>36</v>
@@ -2848,15 +2920,15 @@
         <v>4</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>36</v>
@@ -2865,41 +2937,49 @@
         <v>4</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
+      <c r="A90" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="s">
-        <v>213</v>
+      <c r="A91" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>36</v>
@@ -2908,32 +2988,32 @@
         <v>4</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="s">
-        <v>219</v>
+      <c r="A93" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>4</v>
+        <v>224</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>36</v>
@@ -2942,24 +3022,32 @@
         <v>4</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
+      <c r="A95" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>36</v>
@@ -2968,15 +3056,15 @@
         <v>4</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>36</v>
@@ -2985,32 +3073,24 @@
         <v>4</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C98" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>232</v>
-      </c>
+      <c r="A98" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
     </row>
     <row r="99">
       <c r="A99" s="15" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>36</v>
@@ -3019,15 +3099,15 @@
         <v>4</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>36</v>
@@ -3036,10 +3116,138 @@
         <v>4</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>237</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3059,8 +3267,8 @@
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A103:E103"/>
   </mergeCells>
   <dataValidations count="20">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
@@ -3357,7 +3565,7 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B83:B83</xm:sqref>
+          <xm:sqref>B91:B91</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3383,139 +3591,139 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>121</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>36</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>121</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>36</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>121</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>36</v>
@@ -3533,7 +3741,7 @@
         <v>36</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
@@ -4144,122 +4352,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4284,42 +4492,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -4327,10 +4535,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>36</v>
@@ -4338,10 +4546,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>36</v>
@@ -4519,42 +4727,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -4562,10 +4770,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
